--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0788</v>
+        <v>0.0591</v>
       </c>
       <c r="E2">
-        <v>0.126</v>
+        <v>-0.02</v>
       </c>
       <c r="G2">
-        <v>0.3090301003344482</v>
+        <v>0.3379310344827586</v>
       </c>
       <c r="H2">
-        <v>0.3090301003344482</v>
+        <v>0.3379310344827586</v>
       </c>
       <c r="I2">
-        <v>0.2357859531772575</v>
+        <v>0.1848806366047746</v>
       </c>
       <c r="J2">
-        <v>0.1840280610163961</v>
+        <v>0.1582569403373396</v>
       </c>
       <c r="K2">
-        <v>5.45</v>
+        <v>5.85</v>
       </c>
       <c r="L2">
-        <v>0.1822742474916388</v>
+        <v>0.1551724137931034</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>0.821</v>
       </c>
       <c r="N2">
-        <v>0.08875739644970415</v>
+        <v>0.02189333333333333</v>
       </c>
       <c r="O2">
-        <v>0.5504587155963303</v>
+        <v>0.1403418803418803</v>
       </c>
       <c r="P2">
-        <v>3</v>
+        <v>0.821</v>
       </c>
       <c r="Q2">
-        <v>0.08875739644970415</v>
+        <v>0.02189333333333333</v>
       </c>
       <c r="R2">
-        <v>0.5504587155963303</v>
+        <v>0.1403418803418803</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.1</v>
+        <v>1.094</v>
       </c>
       <c r="V2">
-        <v>0.03254437869822486</v>
+        <v>0.02917333333333333</v>
       </c>
       <c r="W2">
-        <v>0.2309322033898305</v>
+        <v>0.1453998442887332</v>
       </c>
       <c r="X2">
-        <v>0.122647185274808</v>
+        <v>0.2274912987633871</v>
       </c>
       <c r="Y2">
-        <v>0.1082850181150225</v>
+        <v>-0.08209145447465391</v>
       </c>
       <c r="Z2">
-        <v>1.271853332766174</v>
+        <v>0.9181014538635754</v>
       </c>
       <c r="AA2">
-        <v>0.2340567027262003</v>
+        <v>0.1618035353875657</v>
       </c>
       <c r="AB2">
-        <v>0.1215507008449263</v>
+        <v>0.2253803617129322</v>
       </c>
       <c r="AC2">
-        <v>0.112506001881274</v>
+        <v>-0.06357682632536658</v>
       </c>
       <c r="AD2">
-        <v>0.8129999999999999</v>
+        <v>1.408</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.8129999999999999</v>
+        <v>1.408</v>
       </c>
       <c r="AG2">
-        <v>-0.2870000000000001</v>
+        <v>0.3140000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.0234882847485049</v>
+        <v>0.03618793050272437</v>
       </c>
       <c r="AI2">
-        <v>0.03237367100704814</v>
+        <v>0.0592393133625042</v>
       </c>
       <c r="AJ2">
-        <v>-0.008563840897562144</v>
+        <v>0.008303802824350771</v>
       </c>
       <c r="AK2">
-        <v>-0.01195185940948653</v>
+        <v>0.01384846079209668</v>
       </c>
       <c r="AL2">
-        <v>0.073</v>
+        <v>0.161</v>
       </c>
       <c r="AM2">
-        <v>0.073</v>
+        <v>0.161</v>
       </c>
       <c r="AN2">
-        <v>0.112448132780083</v>
+        <v>0.194744121715076</v>
       </c>
       <c r="AO2">
-        <v>96.57534246575342</v>
+        <v>43.29192546583851</v>
       </c>
       <c r="AP2">
-        <v>-0.03969571230982021</v>
+        <v>0.0434301521438451</v>
       </c>
       <c r="AQ2">
-        <v>96.57534246575342</v>
+        <v>43.29192546583851</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>People's Insurance PLC (COSE:PINS.N0000)</t>
+          <t>LOLC General Insurance PLC (COSE:LGIL.N0000)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,122 +721,247 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.0788</v>
-      </c>
-      <c r="E3">
-        <v>0.126</v>
-      </c>
       <c r="G3">
-        <v>0.3090301003344482</v>
+        <v>0.3260869565217391</v>
       </c>
       <c r="H3">
-        <v>0.3090301003344482</v>
+        <v>0.3260869565217391</v>
       </c>
       <c r="I3">
-        <v>0.2357859531772575</v>
+        <v>0.2130434782608696</v>
       </c>
       <c r="J3">
-        <v>0.1840280610163961</v>
+        <v>0.1977023091325151</v>
       </c>
       <c r="K3">
-        <v>5.45</v>
+        <v>3.88</v>
       </c>
       <c r="L3">
-        <v>0.1822742474916388</v>
+        <v>0.18743961352657</v>
       </c>
       <c r="M3">
-        <v>3</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.08875739644970415</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.5504587155963303</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>3</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.08875739644970415</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.5504587155963303</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>1.1</v>
+        <v>0.823</v>
       </c>
       <c r="V3">
-        <v>0.03254437869822486</v>
+        <v>0.0310566037735849</v>
       </c>
       <c r="W3">
-        <v>0.2309322033898305</v>
+        <v>0.2097297297297297</v>
       </c>
       <c r="X3">
-        <v>0.122647185274808</v>
+        <v>0.2299710914971736</v>
       </c>
       <c r="Y3">
-        <v>0.1082850181150225</v>
+        <v>-0.0202413617674439</v>
       </c>
       <c r="Z3">
-        <v>1.271853332766174</v>
+        <v>1.214076246334311</v>
       </c>
       <c r="AA3">
-        <v>0.2340567027262003</v>
+        <v>0.2400256773632294</v>
       </c>
       <c r="AB3">
-        <v>0.1215507008449263</v>
+        <v>0.2266008422195379</v>
       </c>
       <c r="AC3">
-        <v>0.112506001881274</v>
+        <v>0.0134248351436915</v>
       </c>
       <c r="AD3">
-        <v>0.8129999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.8129999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="AG3">
-        <v>-0.2870000000000001</v>
+        <v>0.4470000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.0234882847485049</v>
+        <v>0.04573280518545193</v>
       </c>
       <c r="AI3">
-        <v>0.03237367100704814</v>
+        <v>0.120607787274454</v>
       </c>
       <c r="AJ3">
-        <v>-0.008563840897562144</v>
+        <v>0.01658811741566779</v>
       </c>
       <c r="AK3">
-        <v>-0.01195185940948653</v>
+        <v>0.04604924281446379</v>
       </c>
       <c r="AL3">
-        <v>0.073</v>
+        <v>0.109</v>
       </c>
       <c r="AM3">
-        <v>0.073</v>
+        <v>0.109</v>
       </c>
       <c r="AN3">
-        <v>0.112448132780083</v>
+        <v>0.2778993435448577</v>
       </c>
       <c r="AO3">
-        <v>96.57534246575342</v>
+        <v>40.45871559633028</v>
       </c>
       <c r="AP3">
-        <v>-0.03969571230982021</v>
+        <v>0.09781181619256019</v>
       </c>
       <c r="AQ3">
-        <v>96.57534246575342</v>
+        <v>40.45871559633028</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>People's Insurance PLC (COSE:PINS.N0000)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>0.0591</v>
+      </c>
+      <c r="E4">
+        <v>-0.02</v>
+      </c>
+      <c r="G4">
+        <v>0.3523529411764706</v>
+      </c>
+      <c r="H4">
+        <v>0.3523529411764706</v>
+      </c>
+      <c r="I4">
+        <v>0.1505882352941177</v>
+      </c>
+      <c r="J4">
+        <v>0.1180611764705883</v>
+      </c>
+      <c r="K4">
+        <v>1.97</v>
+      </c>
+      <c r="L4">
+        <v>0.1158823529411765</v>
+      </c>
+      <c r="M4">
+        <v>0.821</v>
+      </c>
+      <c r="N4">
+        <v>0.07463636363636363</v>
+      </c>
+      <c r="O4">
+        <v>0.416751269035533</v>
+      </c>
+      <c r="P4">
+        <v>0.821</v>
+      </c>
+      <c r="Q4">
+        <v>0.07463636363636363</v>
+      </c>
+      <c r="R4">
+        <v>0.416751269035533</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.271</v>
+      </c>
+      <c r="V4">
+        <v>0.02463636363636364</v>
+      </c>
+      <c r="W4">
+        <v>0.08106995884773663</v>
+      </c>
+      <c r="X4">
+        <v>0.2250115060296006</v>
+      </c>
+      <c r="Y4">
+        <v>-0.1439415471818639</v>
+      </c>
+      <c r="Z4">
+        <v>0.7079498604922334</v>
+      </c>
+      <c r="AA4">
+        <v>0.08358139341190189</v>
+      </c>
+      <c r="AB4">
+        <v>0.2241598812063265</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1405784877944247</v>
+      </c>
+      <c r="AD4">
+        <v>0.138</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0.138</v>
+      </c>
+      <c r="AG4">
+        <v>-0.133</v>
+      </c>
+      <c r="AH4">
+        <v>0.01239001616089065</v>
+      </c>
+      <c r="AI4">
+        <v>0.01042453542831243</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.01223888837765713</v>
+      </c>
+      <c r="AK4">
+        <v>-0.01025680573764171</v>
+      </c>
+      <c r="AL4">
+        <v>0.052</v>
+      </c>
+      <c r="AM4">
+        <v>0.052</v>
+      </c>
+      <c r="AN4">
+        <v>0.0518796992481203</v>
+      </c>
+      <c r="AO4">
+        <v>49.23076923076923</v>
+      </c>
+      <c r="AP4">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ4">
+        <v>49.23076923076923</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sri_lanka/sri_lanka_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/sri_lanka/sri_lanka_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0591</v>
+        <v>0.0361</v>
       </c>
       <c r="E2">
-        <v>-0.02</v>
+        <v>-0.0351</v>
       </c>
       <c r="G2">
-        <v>0.3379310344827586</v>
+        <v>0.1559183673469388</v>
       </c>
       <c r="H2">
-        <v>0.3379310344827586</v>
+        <v>0.1559183673469388</v>
       </c>
       <c r="I2">
-        <v>0.1848806366047746</v>
+        <v>0.1410204081632653</v>
       </c>
       <c r="J2">
-        <v>0.1582569403373396</v>
+        <v>0.09739053225098813</v>
       </c>
       <c r="K2">
-        <v>5.85</v>
+        <v>4.46</v>
       </c>
       <c r="L2">
-        <v>0.1551724137931034</v>
+        <v>0.0910204081632653</v>
       </c>
       <c r="M2">
-        <v>0.821</v>
+        <v>0.62</v>
       </c>
       <c r="N2">
-        <v>0.02189333333333333</v>
+        <v>0.01469194312796208</v>
       </c>
       <c r="O2">
-        <v>0.1403418803418803</v>
+        <v>0.1390134529147982</v>
       </c>
       <c r="P2">
-        <v>0.821</v>
+        <v>0.62</v>
       </c>
       <c r="Q2">
-        <v>0.02189333333333333</v>
+        <v>0.01469194312796208</v>
       </c>
       <c r="R2">
-        <v>0.1403418803418803</v>
+        <v>0.1390134529147982</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>1.094</v>
+        <v>2.108</v>
       </c>
       <c r="V2">
-        <v>0.02917333333333333</v>
+        <v>0.04995260663507109</v>
       </c>
       <c r="W2">
-        <v>0.1453998442887332</v>
+        <v>0.2126473546238438</v>
       </c>
       <c r="X2">
-        <v>0.2274912987633871</v>
+        <v>0.1908678055798713</v>
       </c>
       <c r="Y2">
-        <v>-0.08209145447465391</v>
+        <v>0.02177954904397253</v>
       </c>
       <c r="Z2">
-        <v>0.9181014538635754</v>
+        <v>2.161065537620182</v>
       </c>
       <c r="AA2">
-        <v>0.1618035353875657</v>
+        <v>0.2229588626051747</v>
       </c>
       <c r="AB2">
-        <v>0.2253803617129322</v>
+        <v>0.1882788832317072</v>
       </c>
       <c r="AC2">
-        <v>-0.06357682632536658</v>
+        <v>0.03467997937346746</v>
       </c>
       <c r="AD2">
-        <v>1.408</v>
+        <v>2.358</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.408</v>
+        <v>2.358</v>
       </c>
       <c r="AG2">
-        <v>0.3140000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="AH2">
-        <v>0.03618793050272437</v>
+        <v>0.0529197899367117</v>
       </c>
       <c r="AI2">
-        <v>0.0592393133625042</v>
+        <v>0.06099643023436289</v>
       </c>
       <c r="AJ2">
-        <v>0.008303802824350771</v>
+        <v>0.005889281507656065</v>
       </c>
       <c r="AK2">
-        <v>0.01384846079209668</v>
+        <v>0.006839945280437757</v>
       </c>
       <c r="AL2">
-        <v>0.161</v>
+        <v>0.546</v>
       </c>
       <c r="AM2">
-        <v>0.161</v>
+        <v>0.546</v>
       </c>
       <c r="AN2">
-        <v>0.194744121715076</v>
+        <v>0.3302521008403362</v>
       </c>
       <c r="AO2">
-        <v>43.29192546583851</v>
+        <v>12.65567765567766</v>
       </c>
       <c r="AP2">
-        <v>0.0434301521438451</v>
+        <v>0.0350140056022409</v>
       </c>
       <c r="AQ2">
-        <v>43.29192546583851</v>
+        <v>12.65567765567766</v>
       </c>
     </row>
     <row r="3">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.3260869565217391</v>
+        <v>0.1592592592592593</v>
       </c>
       <c r="H3">
-        <v>0.3260869565217391</v>
+        <v>0.1592592592592593</v>
       </c>
       <c r="I3">
-        <v>0.2130434782608696</v>
+        <v>0.1218855218855219</v>
       </c>
       <c r="J3">
-        <v>0.1977023091325151</v>
+        <v>0.09761789552208715</v>
       </c>
       <c r="K3">
-        <v>3.88</v>
+        <v>2.68</v>
       </c>
       <c r="L3">
-        <v>0.18743961352657</v>
+        <v>0.09023569023569024</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,73 +761,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.823</v>
+        <v>1.74</v>
       </c>
       <c r="V3">
-        <v>0.0310566037735849</v>
+        <v>0.06170212765957447</v>
       </c>
       <c r="W3">
-        <v>0.2097297297297297</v>
+        <v>0.2894168466522679</v>
       </c>
       <c r="X3">
-        <v>0.2299710914971736</v>
+        <v>0.1920814006531746</v>
       </c>
       <c r="Y3">
-        <v>-0.0202413617674439</v>
+        <v>0.09733544599909327</v>
       </c>
       <c r="Z3">
-        <v>1.214076246334311</v>
+        <v>3.059647676934171</v>
       </c>
       <c r="AA3">
-        <v>0.2400256773632294</v>
+        <v>0.2986763672613565</v>
       </c>
       <c r="AB3">
-        <v>0.2266008422195379</v>
+        <v>0.1888708663014338</v>
       </c>
       <c r="AC3">
-        <v>0.0134248351436915</v>
+        <v>0.1098055009599227</v>
       </c>
       <c r="AD3">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.27</v>
+        <v>1.78</v>
       </c>
       <c r="AG3">
-        <v>0.4470000000000001</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="AH3">
-        <v>0.04573280518545193</v>
+        <v>0.05937291527685123</v>
       </c>
       <c r="AI3">
-        <v>0.120607787274454</v>
+        <v>0.08135283363802559</v>
       </c>
       <c r="AJ3">
-        <v>0.01658811741566779</v>
+        <v>0.001416430594900851</v>
       </c>
       <c r="AK3">
-        <v>0.04604924281446379</v>
+        <v>0.001986097318768621</v>
       </c>
       <c r="AL3">
-        <v>0.109</v>
+        <v>0.311</v>
       </c>
       <c r="AM3">
-        <v>0.109</v>
+        <v>0.311</v>
       </c>
       <c r="AN3">
-        <v>0.2778993435448577</v>
+        <v>0.473404255319149</v>
       </c>
       <c r="AO3">
-        <v>40.45871559633028</v>
+        <v>11.63987138263666</v>
       </c>
       <c r="AP3">
-        <v>0.09781181619256019</v>
+        <v>0.01063829787234044</v>
       </c>
       <c r="AQ3">
-        <v>40.45871559633028</v>
+        <v>11.63987138263666</v>
       </c>
     </row>
     <row r="4">
@@ -847,46 +847,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0591</v>
+        <v>0.0361</v>
       </c>
       <c r="E4">
-        <v>-0.02</v>
+        <v>-0.0351</v>
       </c>
       <c r="G4">
-        <v>0.3523529411764706</v>
+        <v>0.1507772020725389</v>
       </c>
       <c r="H4">
-        <v>0.3523529411764706</v>
+        <v>0.1507772020725389</v>
       </c>
       <c r="I4">
-        <v>0.1505882352941177</v>
+        <v>0.1704663212435233</v>
       </c>
       <c r="J4">
-        <v>0.1180611764705883</v>
+        <v>0.09892635691837252</v>
       </c>
       <c r="K4">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="L4">
-        <v>0.1158823529411765</v>
+        <v>0.09222797927461139</v>
       </c>
       <c r="M4">
-        <v>0.821</v>
+        <v>0.62</v>
       </c>
       <c r="N4">
-        <v>0.07463636363636363</v>
+        <v>0.04428571428571428</v>
       </c>
       <c r="O4">
-        <v>0.416751269035533</v>
+        <v>0.3483146067415731</v>
       </c>
       <c r="P4">
-        <v>0.821</v>
+        <v>0.62</v>
       </c>
       <c r="Q4">
-        <v>0.07463636363636363</v>
+        <v>0.04428571428571428</v>
       </c>
       <c r="R4">
-        <v>0.416751269035533</v>
+        <v>0.3483146067415731</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -895,73 +895,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.271</v>
+        <v>0.368</v>
       </c>
       <c r="V4">
-        <v>0.02463636363636364</v>
+        <v>0.02628571428571428</v>
       </c>
       <c r="W4">
-        <v>0.08106995884773663</v>
+        <v>0.1358778625954198</v>
       </c>
       <c r="X4">
-        <v>0.2250115060296006</v>
+        <v>0.1896542105065681</v>
       </c>
       <c r="Y4">
-        <v>-0.1439415471818639</v>
+        <v>-0.05377634791114821</v>
       </c>
       <c r="Z4">
-        <v>0.7079498604922334</v>
+        <v>1.488393614560037</v>
       </c>
       <c r="AA4">
-        <v>0.08358139341190189</v>
+        <v>0.1472413579489928</v>
       </c>
       <c r="AB4">
-        <v>0.2241598812063265</v>
+        <v>0.1876869001619806</v>
       </c>
       <c r="AC4">
-        <v>-0.1405784877944247</v>
+        <v>-0.0404455422129878</v>
       </c>
       <c r="AD4">
-        <v>0.138</v>
+        <v>0.578</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.138</v>
+        <v>0.578</v>
       </c>
       <c r="AG4">
-        <v>-0.133</v>
+        <v>0.21</v>
       </c>
       <c r="AH4">
-        <v>0.01239001616089065</v>
+        <v>0.03964878584167924</v>
       </c>
       <c r="AI4">
-        <v>0.01042453542831243</v>
+        <v>0.03444987483609489</v>
       </c>
       <c r="AJ4">
-        <v>-0.01223888837765713</v>
+        <v>0.01477832512315271</v>
       </c>
       <c r="AK4">
-        <v>-0.01025680573764171</v>
+        <v>0.01279707495429616</v>
       </c>
       <c r="AL4">
-        <v>0.052</v>
+        <v>0.235</v>
       </c>
       <c r="AM4">
-        <v>0.052</v>
+        <v>0.235</v>
       </c>
       <c r="AN4">
-        <v>0.0518796992481203</v>
+        <v>0.1710059171597633</v>
       </c>
       <c r="AO4">
-        <v>49.23076923076923</v>
+        <v>14</v>
       </c>
       <c r="AP4">
-        <v>-0.05</v>
+        <v>0.06213017751479289</v>
       </c>
       <c r="AQ4">
-        <v>49.23076923076923</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
